--- a/File tài chính cá nhân/Danh mục đầu tư cá nhân.xlsx
+++ b/File tài chính cá nhân/Danh mục đầu tư cá nhân.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeVeL infinity\Desktop\File tài chính cá nhân\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeVeL infinity\Desktop\BackUp\backup-PC\File tài chính cá nhân\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101CF825-116E-4531-8F34-DD92C45E473F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB375904-413F-4F12-B5BE-4EF32973CCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{01424E0D-5617-48C9-A47B-ABAE5C326979}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{01424E0D-5617-48C9-A47B-ABAE5C326979}"/>
   </bookViews>
   <sheets>
     <sheet name="FCO" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>NẠP FCO</t>
   </si>
@@ -150,6 +150,27 @@
   </si>
   <si>
     <t>Ngày 07_ TK NH</t>
+  </si>
+  <si>
+    <t>LƯƠNG 25</t>
+  </si>
+  <si>
+    <t>LƯƠNG 10</t>
+  </si>
+  <si>
+    <t>NGÀY 07</t>
+  </si>
+  <si>
+    <t>THƯỞNG 06/2026</t>
+  </si>
+  <si>
+    <t>NGÀY 12</t>
+  </si>
+  <si>
+    <t>KÌ T5</t>
+  </si>
+  <si>
+    <t>KÌ T6</t>
   </si>
 </sst>
 </file>
@@ -1149,10 +1170,10 @@
                 <c:formatCode>[$¥-411]#,##0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>410120.48192771082</c:v>
+                  <c:v>540240.96385542164</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2589879.5180722894</c:v>
+                  <c:v>-2459759.0361445784</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2142,14 +2163,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E47ADB-D9E0-48C5-AF00-F0C27A9CBC6C}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="14.296875" defaultRowHeight="22.8"/>
+  <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="23.25"/>
   <cols>
     <col min="1" max="1" width="19" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.09765625" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="14.296875" style="3"/>
+    <col min="2" max="2" width="25.125" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="14.25" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" thickTop="1" thickBot="1">
+    <row r="1" spans="1:2" ht="24.75" thickTop="1" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2158,7 +2179,7 @@
         <v>62414710</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="24" thickTop="1" thickBot="1">
+    <row r="2" spans="1:2" ht="24.75" thickTop="1" thickBot="1">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2167,7 +2188,7 @@
         <v>32764710</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="24" thickTop="1" thickBot="1">
+    <row r="3" spans="1:2" ht="24.75" thickTop="1" thickBot="1">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -2175,7 +2196,7 @@
         <v>29650000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="23.4" thickTop="1"/>
+    <row r="4" spans="1:2" ht="24" thickTop="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2184,17 +2205,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A75988-4B25-4375-8D7D-9D83919DB7AD}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="22.59765625" defaultRowHeight="25.2" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="22.625" defaultRowHeight="25.15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="49.69921875" style="1" customWidth="1"/>
-    <col min="2" max="3" width="22.59765625" style="1"/>
-    <col min="4" max="5" width="29.09765625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.59765625" style="1"/>
-    <col min="7" max="9" width="20.796875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="22.59765625" style="1"/>
+    <col min="1" max="1" width="55.25" style="1" customWidth="1"/>
+    <col min="2" max="3" width="22.625" style="1"/>
+    <col min="4" max="5" width="29.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.625" style="1"/>
+    <col min="7" max="9" width="20.75" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="22.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="25.2" customHeight="1" thickTop="1" thickBot="1">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
@@ -2206,12 +2227,12 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="25.2" customHeight="1" thickTop="1" thickBot="1">
+    <row r="2" spans="1:9" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="25.2" customHeight="1" thickTop="1" thickBot="1">
+    <row r="3" spans="1:9" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
       <c r="A3" s="8" t="s">
         <v>5</v>
       </c>
@@ -2223,7 +2244,7 @@
       </c>
       <c r="E3" s="54"/>
     </row>
-    <row r="4" spans="1:9" ht="25.2" customHeight="1" thickTop="1" thickBot="1">
+    <row r="4" spans="1:9" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
       <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
@@ -2240,7 +2261,7 @@
       <c r="H4" s="58"/>
       <c r="I4" s="58"/>
     </row>
-    <row r="5" spans="1:9" ht="25.2" customHeight="1" thickTop="1" thickBot="1">
+    <row r="5" spans="1:9" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
       <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
@@ -2263,7 +2284,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="25.2" customHeight="1" thickTop="1" thickBot="1">
+    <row r="6" spans="1:9" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -2281,14 +2302,14 @@
       </c>
       <c r="H6" s="46">
         <f>SUM('NĂM 1 (01 05 2026 - 01 05 2027)'!F4:F6)</f>
-        <v>410120.48192771082</v>
+        <v>540240.96385542164</v>
       </c>
       <c r="I6" s="49">
         <f>H6-G6</f>
-        <v>-2589879.5180722894</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="25.2" customHeight="1" thickTop="1" thickBot="1">
+        <v>-2459759.0361445784</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
       <c r="C7" s="13" t="s">
         <v>14</v>
       </c>
@@ -2300,7 +2321,7 @@
         <v>1567500000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="25.2" customHeight="1" thickTop="1" thickBot="1">
+    <row r="8" spans="1:9" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
       <c r="C8" s="16" t="s">
         <v>15</v>
       </c>
@@ -2329,36 +2350,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F354D7CF-DB3F-451C-84E8-30113D9CFD93}">
   <dimension ref="A1:Y56"/>
-  <sheetFormatPr defaultRowHeight="28.8" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="28.9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.5" style="21" customWidth="1"/>
-    <col min="2" max="2" width="20.3984375" style="21" customWidth="1"/>
-    <col min="3" max="3" width="20.796875" style="21" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" style="21"/>
-    <col min="5" max="5" width="27.59765625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="20.375" style="21" customWidth="1"/>
+    <col min="3" max="3" width="20.75" style="21" customWidth="1"/>
+    <col min="4" max="4" width="8.75" style="21"/>
+    <col min="5" max="5" width="27.625" style="21" customWidth="1"/>
     <col min="6" max="6" width="15" style="21" customWidth="1"/>
-    <col min="7" max="7" width="16.8984375" style="21" customWidth="1"/>
-    <col min="8" max="8" width="8.796875" style="21"/>
-    <col min="9" max="9" width="19.19921875" style="21" customWidth="1"/>
-    <col min="10" max="10" width="19.19921875" style="43" customWidth="1"/>
-    <col min="11" max="11" width="19.19921875" style="44" customWidth="1"/>
+    <col min="7" max="7" width="16.875" style="21" customWidth="1"/>
+    <col min="8" max="8" width="8.75" style="21"/>
+    <col min="9" max="9" width="19.25" style="21" customWidth="1"/>
+    <col min="10" max="10" width="19.25" style="43" customWidth="1"/>
+    <col min="11" max="11" width="19.25" style="44" customWidth="1"/>
     <col min="12" max="12" width="16.5" style="37" customWidth="1"/>
     <col min="13" max="13" width="14.5" style="21" customWidth="1"/>
-    <col min="14" max="14" width="8.796875" style="21"/>
-    <col min="15" max="15" width="19.19921875" style="21" customWidth="1"/>
-    <col min="16" max="16" width="19.19921875" style="43" customWidth="1"/>
-    <col min="17" max="17" width="19.19921875" style="44" customWidth="1"/>
-    <col min="18" max="18" width="19.09765625" style="37" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="21"/>
+    <col min="15" max="15" width="19.25" style="21" customWidth="1"/>
+    <col min="16" max="16" width="19.25" style="43" customWidth="1"/>
+    <col min="17" max="17" width="19.25" style="44" customWidth="1"/>
+    <col min="18" max="18" width="19.125" style="37" customWidth="1"/>
     <col min="19" max="19" width="14.5" style="21" customWidth="1"/>
-    <col min="20" max="20" width="8.796875" style="21"/>
-    <col min="21" max="21" width="19.19921875" style="21" customWidth="1"/>
+    <col min="20" max="20" width="8.75" style="21"/>
+    <col min="21" max="21" width="19.25" style="21" customWidth="1"/>
     <col min="22" max="23" width="21" style="45" customWidth="1"/>
-    <col min="24" max="24" width="19.09765625" style="37" customWidth="1"/>
-    <col min="25" max="25" width="17.59765625" style="21" customWidth="1"/>
-    <col min="26" max="16384" width="8.796875" style="21"/>
+    <col min="24" max="24" width="19.125" style="37" customWidth="1"/>
+    <col min="25" max="25" width="17.625" style="21" customWidth="1"/>
+    <col min="26" max="16384" width="8.75" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="1" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1" s="67" t="s">
         <v>19</v>
       </c>
@@ -2407,7 +2428,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="2" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="67"/>
       <c r="B2" s="19" t="s">
         <v>1</v>
@@ -2463,7 +2484,7 @@
       </c>
       <c r="X2" s="21"/>
     </row>
-    <row r="3" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="3" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="C3" s="50">
         <f>C1+C2*165</f>
         <v>145314863</v>
@@ -2475,15 +2496,11 @@
       <c r="G3" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="31">
-        <v>46152</v>
-      </c>
-      <c r="J3" s="23">
-        <v>30000</v>
-      </c>
+      <c r="I3" s="31"/>
+      <c r="J3" s="23"/>
       <c r="K3" s="32">
         <f>SUM(J3:J28)</f>
-        <v>80000</v>
+        <v>180000</v>
       </c>
       <c r="L3" s="22" t="s">
         <v>33</v>
@@ -2491,60 +2508,62 @@
       <c r="M3" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="31">
-        <v>45763</v>
-      </c>
-      <c r="P3" s="23">
-        <v>50000</v>
-      </c>
+      <c r="O3" s="31"/>
+      <c r="P3" s="23"/>
       <c r="Q3" s="32">
         <f>SUM(P3:P28)</f>
         <v>300000</v>
       </c>
       <c r="R3" s="21"/>
-      <c r="U3" s="31">
-        <v>45803</v>
-      </c>
-      <c r="V3" s="24">
-        <v>5000000</v>
-      </c>
+      <c r="U3" s="31"/>
+      <c r="V3" s="24"/>
       <c r="W3" s="33">
         <f>SUM(V3:V28)</f>
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="X3" s="21"/>
     </row>
-    <row r="4" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="4" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="E4" s="34" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="23">
         <f>K3</f>
-        <v>80000</v>
+        <v>180000</v>
       </c>
       <c r="G4" s="35">
         <f>F4*165</f>
-        <v>13200000</v>
+        <v>29700000</v>
       </c>
       <c r="I4" s="31">
-        <v>46167</v>
+        <v>46152</v>
       </c>
       <c r="J4" s="23">
-        <v>20000</v>
-      </c>
-      <c r="K4" s="36"/>
+        <v>30000</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>42</v>
+      </c>
       <c r="O4" s="31">
-        <v>45774</v>
+        <v>46128</v>
       </c>
       <c r="P4" s="23">
-        <v>100000</v>
-      </c>
-      <c r="Q4" s="36"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="35"/>
-    </row>
-    <row r="5" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+        <v>50000</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="31">
+        <v>46168</v>
+      </c>
+      <c r="V4" s="24">
+        <v>5000000</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="E5" s="34" t="s">
         <v>25</v>
       </c>
@@ -2557,61 +2576,91 @@
         <v>49500000</v>
       </c>
       <c r="I5" s="31">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="J5" s="23">
-        <v>30000</v>
-      </c>
-      <c r="K5" s="36"/>
+        <v>20000</v>
+      </c>
+      <c r="K5" s="36" t="s">
+        <v>41</v>
+      </c>
       <c r="O5" s="31">
-        <v>46158</v>
+        <v>46139</v>
       </c>
       <c r="P5" s="23">
-        <v>50000</v>
-      </c>
-      <c r="Q5" s="36"/>
-      <c r="U5" s="31"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="35"/>
-    </row>
-    <row r="6" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+        <v>100000</v>
+      </c>
+      <c r="Q5" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="U5" s="31">
+        <v>46183</v>
+      </c>
+      <c r="V5" s="24">
+        <v>5000000</v>
+      </c>
+      <c r="W5" s="35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="E6" s="38" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="39">
         <f>G6/166</f>
-        <v>30120.481927710844</v>
+        <v>60240.963855421687</v>
       </c>
       <c r="G6" s="35">
         <f>W3</f>
-        <v>5000000</v>
-      </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="36"/>
+        <v>10000000</v>
+      </c>
+      <c r="I6" s="31">
+        <v>46182</v>
+      </c>
+      <c r="J6" s="23">
+        <v>30000</v>
+      </c>
+      <c r="K6" s="36" t="s">
+        <v>42</v>
+      </c>
       <c r="O6" s="31">
-        <v>46169</v>
+        <v>46158</v>
       </c>
       <c r="P6" s="23">
-        <v>100000</v>
-      </c>
-      <c r="Q6" s="36"/>
+        <v>50000</v>
+      </c>
+      <c r="Q6" s="36" t="s">
+        <v>45</v>
+      </c>
       <c r="U6" s="31"/>
       <c r="V6" s="24"/>
       <c r="W6" s="35"/>
     </row>
-    <row r="7" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
-      <c r="I7" s="34"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="36"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="36"/>
+    <row r="7" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
+      <c r="I7" s="31">
+        <v>46188</v>
+      </c>
+      <c r="J7" s="23">
+        <v>100000</v>
+      </c>
+      <c r="K7" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="O7" s="31">
+        <v>46169</v>
+      </c>
+      <c r="P7" s="23">
+        <v>100000</v>
+      </c>
+      <c r="Q7" s="36" t="s">
+        <v>43</v>
+      </c>
       <c r="U7" s="34"/>
       <c r="V7" s="24"/>
       <c r="W7" s="35"/>
     </row>
-    <row r="8" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="8" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I8" s="34"/>
       <c r="J8" s="23"/>
       <c r="K8" s="36"/>
@@ -2622,7 +2671,7 @@
       <c r="V8" s="24"/>
       <c r="W8" s="35"/>
     </row>
-    <row r="9" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="9" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I9" s="34"/>
       <c r="J9" s="23"/>
       <c r="K9" s="36"/>
@@ -2633,7 +2682,7 @@
       <c r="V9" s="24"/>
       <c r="W9" s="35"/>
     </row>
-    <row r="10" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="10" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I10" s="34"/>
       <c r="J10" s="23"/>
       <c r="K10" s="36"/>
@@ -2647,7 +2696,7 @@
       <c r="W10" s="35"/>
       <c r="X10" s="21"/>
     </row>
-    <row r="11" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="11" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I11" s="34"/>
       <c r="J11" s="23"/>
       <c r="K11" s="36"/>
@@ -2661,7 +2710,7 @@
       <c r="W11" s="35"/>
       <c r="X11" s="21"/>
     </row>
-    <row r="12" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="12" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I12" s="34"/>
       <c r="J12" s="23"/>
       <c r="K12" s="36"/>
@@ -2675,7 +2724,7 @@
       <c r="W12" s="35"/>
       <c r="X12" s="21"/>
     </row>
-    <row r="13" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="13" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I13" s="34"/>
       <c r="J13" s="23"/>
       <c r="K13" s="36"/>
@@ -2686,7 +2735,7 @@
       <c r="V13" s="24"/>
       <c r="W13" s="35"/>
     </row>
-    <row r="14" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="14" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I14" s="34"/>
       <c r="J14" s="23"/>
       <c r="K14" s="36"/>
@@ -2697,7 +2746,7 @@
       <c r="V14" s="24"/>
       <c r="W14" s="35"/>
     </row>
-    <row r="15" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="15" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I15" s="34"/>
       <c r="J15" s="23"/>
       <c r="K15" s="36"/>
@@ -2708,7 +2757,7 @@
       <c r="V15" s="24"/>
       <c r="W15" s="35"/>
     </row>
-    <row r="16" spans="1:25" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="16" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I16" s="34"/>
       <c r="J16" s="23"/>
       <c r="K16" s="36"/>
@@ -2719,7 +2768,7 @@
       <c r="V16" s="24"/>
       <c r="W16" s="35"/>
     </row>
-    <row r="17" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="17" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I17" s="34"/>
       <c r="J17" s="23"/>
       <c r="K17" s="36"/>
@@ -2730,7 +2779,7 @@
       <c r="V17" s="24"/>
       <c r="W17" s="35"/>
     </row>
-    <row r="18" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="18" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I18" s="34"/>
       <c r="J18" s="23"/>
       <c r="K18" s="36"/>
@@ -2741,7 +2790,7 @@
       <c r="V18" s="24"/>
       <c r="W18" s="35"/>
     </row>
-    <row r="19" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="19" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I19" s="34"/>
       <c r="J19" s="23"/>
       <c r="K19" s="36"/>
@@ -2752,7 +2801,7 @@
       <c r="V19" s="24"/>
       <c r="W19" s="35"/>
     </row>
-    <row r="20" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="20" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I20" s="34"/>
       <c r="J20" s="23"/>
       <c r="K20" s="36"/>
@@ -2763,7 +2812,7 @@
       <c r="V20" s="24"/>
       <c r="W20" s="35"/>
     </row>
-    <row r="21" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="21" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I21" s="34"/>
       <c r="J21" s="23"/>
       <c r="K21" s="36"/>
@@ -2774,7 +2823,7 @@
       <c r="V21" s="24"/>
       <c r="W21" s="35"/>
     </row>
-    <row r="22" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="22" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I22" s="34"/>
       <c r="J22" s="23"/>
       <c r="K22" s="36"/>
@@ -2785,7 +2834,7 @@
       <c r="V22" s="24"/>
       <c r="W22" s="35"/>
     </row>
-    <row r="23" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="23" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I23" s="34"/>
       <c r="J23" s="23"/>
       <c r="K23" s="36"/>
@@ -2796,7 +2845,7 @@
       <c r="V23" s="24"/>
       <c r="W23" s="35"/>
     </row>
-    <row r="24" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="24" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I24" s="34"/>
       <c r="J24" s="23"/>
       <c r="K24" s="36"/>
@@ -2807,7 +2856,7 @@
       <c r="V24" s="24"/>
       <c r="W24" s="35"/>
     </row>
-    <row r="25" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="25" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I25" s="34"/>
       <c r="J25" s="23"/>
       <c r="K25" s="36"/>
@@ -2818,7 +2867,7 @@
       <c r="V25" s="24"/>
       <c r="W25" s="35"/>
     </row>
-    <row r="26" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="26" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I26" s="34"/>
       <c r="J26" s="23"/>
       <c r="K26" s="36"/>
@@ -2829,7 +2878,7 @@
       <c r="V26" s="24"/>
       <c r="W26" s="35"/>
     </row>
-    <row r="27" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="27" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I27" s="34"/>
       <c r="J27" s="23"/>
       <c r="K27" s="36"/>
@@ -2840,7 +2889,7 @@
       <c r="V27" s="24"/>
       <c r="W27" s="35"/>
     </row>
-    <row r="28" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="28" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I28" s="34"/>
       <c r="J28" s="23"/>
       <c r="K28" s="36"/>
@@ -2851,7 +2900,7 @@
       <c r="V28" s="24"/>
       <c r="W28" s="35"/>
     </row>
-    <row r="29" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="29" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I29" s="34"/>
       <c r="J29" s="23"/>
       <c r="K29" s="36"/>
@@ -2862,7 +2911,7 @@
       <c r="V29" s="24"/>
       <c r="W29" s="35"/>
     </row>
-    <row r="30" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="30" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I30" s="34"/>
       <c r="J30" s="23"/>
       <c r="K30" s="36"/>
@@ -2873,7 +2922,7 @@
       <c r="V30" s="24"/>
       <c r="W30" s="35"/>
     </row>
-    <row r="31" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="31" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I31" s="34"/>
       <c r="J31" s="23"/>
       <c r="K31" s="36"/>
@@ -2884,7 +2933,7 @@
       <c r="V31" s="24"/>
       <c r="W31" s="35"/>
     </row>
-    <row r="32" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="32" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I32" s="34"/>
       <c r="J32" s="23"/>
       <c r="K32" s="36"/>
@@ -2895,7 +2944,7 @@
       <c r="V32" s="24"/>
       <c r="W32" s="35"/>
     </row>
-    <row r="33" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="33" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I33" s="34"/>
       <c r="J33" s="23"/>
       <c r="K33" s="36"/>
@@ -2906,7 +2955,7 @@
       <c r="V33" s="24"/>
       <c r="W33" s="35"/>
     </row>
-    <row r="34" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="34" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I34" s="34"/>
       <c r="J34" s="23"/>
       <c r="K34" s="36"/>
@@ -2917,7 +2966,7 @@
       <c r="V34" s="24"/>
       <c r="W34" s="35"/>
     </row>
-    <row r="35" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="35" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I35" s="34"/>
       <c r="J35" s="23"/>
       <c r="K35" s="36"/>
@@ -2928,7 +2977,7 @@
       <c r="V35" s="24"/>
       <c r="W35" s="35"/>
     </row>
-    <row r="36" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="36" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I36" s="34"/>
       <c r="J36" s="23"/>
       <c r="K36" s="36"/>
@@ -2939,7 +2988,7 @@
       <c r="V36" s="24"/>
       <c r="W36" s="35"/>
     </row>
-    <row r="37" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="37" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I37" s="34"/>
       <c r="J37" s="23"/>
       <c r="K37" s="36"/>
@@ -2950,7 +2999,7 @@
       <c r="V37" s="24"/>
       <c r="W37" s="35"/>
     </row>
-    <row r="38" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="38" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I38" s="34"/>
       <c r="J38" s="23"/>
       <c r="K38" s="36"/>
@@ -2961,7 +3010,7 @@
       <c r="V38" s="24"/>
       <c r="W38" s="35"/>
     </row>
-    <row r="39" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="39" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I39" s="34"/>
       <c r="J39" s="23"/>
       <c r="K39" s="36"/>
@@ -2972,7 +3021,7 @@
       <c r="V39" s="24"/>
       <c r="W39" s="35"/>
     </row>
-    <row r="40" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="40" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I40" s="34"/>
       <c r="J40" s="23"/>
       <c r="K40" s="36"/>
@@ -2983,7 +3032,7 @@
       <c r="V40" s="24"/>
       <c r="W40" s="35"/>
     </row>
-    <row r="41" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="41" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I41" s="34"/>
       <c r="J41" s="23"/>
       <c r="K41" s="36"/>
@@ -2994,7 +3043,7 @@
       <c r="V41" s="24"/>
       <c r="W41" s="35"/>
     </row>
-    <row r="42" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="42" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I42" s="34"/>
       <c r="J42" s="23"/>
       <c r="K42" s="36"/>
@@ -3005,7 +3054,7 @@
       <c r="V42" s="24"/>
       <c r="W42" s="35"/>
     </row>
-    <row r="43" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="43" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I43" s="34"/>
       <c r="J43" s="23"/>
       <c r="K43" s="36"/>
@@ -3016,7 +3065,7 @@
       <c r="V43" s="24"/>
       <c r="W43" s="35"/>
     </row>
-    <row r="44" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="44" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I44" s="34"/>
       <c r="J44" s="23"/>
       <c r="K44" s="36"/>
@@ -3027,7 +3076,7 @@
       <c r="V44" s="24"/>
       <c r="W44" s="35"/>
     </row>
-    <row r="45" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="45" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I45" s="34"/>
       <c r="J45" s="23"/>
       <c r="K45" s="36"/>
@@ -3038,7 +3087,7 @@
       <c r="V45" s="24"/>
       <c r="W45" s="35"/>
     </row>
-    <row r="46" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="46" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I46" s="34"/>
       <c r="J46" s="23"/>
       <c r="K46" s="36"/>
@@ -3049,7 +3098,7 @@
       <c r="V46" s="24"/>
       <c r="W46" s="35"/>
     </row>
-    <row r="47" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="47" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I47" s="34"/>
       <c r="J47" s="23"/>
       <c r="K47" s="36"/>
@@ -3060,7 +3109,7 @@
       <c r="V47" s="24"/>
       <c r="W47" s="35"/>
     </row>
-    <row r="48" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="48" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I48" s="34"/>
       <c r="J48" s="23"/>
       <c r="K48" s="36"/>
@@ -3071,7 +3120,7 @@
       <c r="V48" s="24"/>
       <c r="W48" s="35"/>
     </row>
-    <row r="49" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="49" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I49" s="34"/>
       <c r="J49" s="23"/>
       <c r="K49" s="36"/>
@@ -3082,7 +3131,7 @@
       <c r="V49" s="24"/>
       <c r="W49" s="35"/>
     </row>
-    <row r="50" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="50" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I50" s="34"/>
       <c r="J50" s="23"/>
       <c r="K50" s="36"/>
@@ -3093,7 +3142,7 @@
       <c r="V50" s="24"/>
       <c r="W50" s="35"/>
     </row>
-    <row r="51" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="51" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I51" s="34"/>
       <c r="J51" s="23"/>
       <c r="K51" s="36"/>
@@ -3104,7 +3153,7 @@
       <c r="V51" s="24"/>
       <c r="W51" s="35"/>
     </row>
-    <row r="52" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="52" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I52" s="34"/>
       <c r="J52" s="23"/>
       <c r="K52" s="36"/>
@@ -3115,7 +3164,7 @@
       <c r="V52" s="24"/>
       <c r="W52" s="35"/>
     </row>
-    <row r="53" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="53" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I53" s="34"/>
       <c r="J53" s="23"/>
       <c r="K53" s="36"/>
@@ -3126,7 +3175,7 @@
       <c r="V53" s="24"/>
       <c r="W53" s="35"/>
     </row>
-    <row r="54" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="54" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I54" s="34"/>
       <c r="J54" s="23"/>
       <c r="K54" s="36"/>
@@ -3137,7 +3186,7 @@
       <c r="V54" s="24"/>
       <c r="W54" s="35"/>
     </row>
-    <row r="55" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="55" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I55" s="34"/>
       <c r="J55" s="23"/>
       <c r="K55" s="36"/>
@@ -3148,7 +3197,7 @@
       <c r="V55" s="24"/>
       <c r="W55" s="35"/>
     </row>
-    <row r="56" spans="9:23" ht="28.8" customHeight="1" thickTop="1" thickBot="1">
+    <row r="56" spans="9:23" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
       <c r="I56" s="38"/>
       <c r="J56" s="39"/>
       <c r="K56" s="40"/>

--- a/File tài chính cá nhân/Danh mục đầu tư cá nhân.xlsx
+++ b/File tài chính cá nhân/Danh mục đầu tư cá nhân.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeVeL infinity\Desktop\BackUp\backup-PC\File tài chính cá nhân\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB375904-413F-4F12-B5BE-4EF32973CCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3175FC29-E185-4494-9888-48E0B1DB1E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{01424E0D-5617-48C9-A47B-ABAE5C326979}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
   <si>
     <t>NẠP FCO</t>
   </si>
@@ -1170,10 +1170,10 @@
                 <c:formatCode>[$¥-411]#,##0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>540240.96385542164</c:v>
+                  <c:v>560240.96385542164</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2459759.0361445784</c:v>
+                  <c:v>-2439759.0361445784</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2302,11 +2302,11 @@
       </c>
       <c r="H6" s="46">
         <f>SUM('NĂM 1 (01 05 2026 - 01 05 2027)'!F4:F6)</f>
-        <v>540240.96385542164</v>
+        <v>560240.96385542164</v>
       </c>
       <c r="I6" s="49">
         <f>H6-G6</f>
-        <v>-2459759.0361445784</v>
+        <v>-2439759.0361445784</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
@@ -2500,7 +2500,7 @@
       <c r="J3" s="23"/>
       <c r="K3" s="32">
         <f>SUM(J3:J28)</f>
-        <v>180000</v>
+        <v>200000</v>
       </c>
       <c r="L3" s="22" t="s">
         <v>33</v>
@@ -2529,11 +2529,11 @@
       </c>
       <c r="F4" s="23">
         <f>K3</f>
-        <v>180000</v>
+        <v>200000</v>
       </c>
       <c r="G4" s="35">
         <f>F4*165</f>
-        <v>29700000</v>
+        <v>33000000</v>
       </c>
       <c r="I4" s="31">
         <v>46152</v>
@@ -2661,9 +2661,15 @@
       <c r="W7" s="35"/>
     </row>
     <row r="8" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
-      <c r="I8" s="34"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="36"/>
+      <c r="I8" s="31">
+        <v>46188</v>
+      </c>
+      <c r="J8" s="23">
+        <v>20000</v>
+      </c>
+      <c r="K8" s="36" t="s">
+        <v>44</v>
+      </c>
       <c r="O8" s="34"/>
       <c r="P8" s="23"/>
       <c r="Q8" s="36"/>

--- a/File tài chính cá nhân/Danh mục đầu tư cá nhân.xlsx
+++ b/File tài chính cá nhân/Danh mục đầu tư cá nhân.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LeVeL infinity\Desktop\BackUp\backup-PC\File tài chính cá nhân\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3175FC29-E185-4494-9888-48E0B1DB1E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F788B492-C342-4DBD-B4B0-9ADFD38009B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{01424E0D-5617-48C9-A47B-ABAE5C326979}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
     <t>NẠP FCO</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>KÌ T6</t>
+  </si>
+  <si>
+    <t>LƯƠNG 5/25</t>
   </si>
 </sst>
 </file>
@@ -1170,10 +1173,10 @@
                 <c:formatCode>[$¥-411]#,##0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>560240.96385542164</c:v>
+                  <c:v>620240.96385542164</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2439759.0361445784</c:v>
+                  <c:v>-2379759.0361445784</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2302,11 +2305,11 @@
       </c>
       <c r="H6" s="46">
         <f>SUM('NĂM 1 (01 05 2026 - 01 05 2027)'!F4:F6)</f>
-        <v>560240.96385542164</v>
+        <v>620240.96385542164</v>
       </c>
       <c r="I6" s="49">
         <f>H6-G6</f>
-        <v>-2439759.0361445784</v>
+        <v>-2379759.0361445784</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="25.15" customHeight="1" thickTop="1" thickBot="1">
@@ -2500,7 +2503,7 @@
       <c r="J3" s="23"/>
       <c r="K3" s="32">
         <f>SUM(J3:J28)</f>
-        <v>200000</v>
+        <v>260000</v>
       </c>
       <c r="L3" s="22" t="s">
         <v>33</v>
@@ -2529,11 +2532,11 @@
       </c>
       <c r="F4" s="23">
         <f>K3</f>
-        <v>200000</v>
+        <v>260000</v>
       </c>
       <c r="G4" s="35">
         <f>F4*165</f>
-        <v>33000000</v>
+        <v>42900000</v>
       </c>
       <c r="I4" s="31">
         <v>46152</v>
@@ -2678,9 +2681,15 @@
       <c r="W8" s="35"/>
     </row>
     <row r="9" spans="1:25" ht="28.9" customHeight="1" thickTop="1" thickBot="1">
-      <c r="I9" s="34"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="36"/>
+      <c r="I9" s="31">
+        <v>46198</v>
+      </c>
+      <c r="J9" s="23">
+        <v>60000</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>48</v>
+      </c>
       <c r="O9" s="34"/>
       <c r="P9" s="23"/>
       <c r="Q9" s="36"/>
